--- a/docs/model/dona-building-unit-model-draft.xlsx
+++ b/docs/model/dona-building-unit-model-draft.xlsx
@@ -15,11 +15,11 @@
     <sheet name="DECISIONS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ENTITIES'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RELATIONSHIPS'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FIELDS'!$A$1:$G$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ADMIN VIEWS'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DECISIONS'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ENTITIES'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RELATIONSHIPS'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FIELDS'!$A$1:$G$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ADMIN VIEWS'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DECISIONS'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B31"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3 September 2026. Minimal fields on purpose — the goal of this pass is to get the relationships right, then add fields on top of a shape that already holds. Nothing here is published; this workbook is handed over as a file.</t>
+          <t>3 September 2026, with the document-type catalogue added 7 September 2026 (E15, E16, R17, R18, A8). Minimal fields on purpose — the goal of this pass is to get the relationships right, then add fields on top of a shape that already holds. Nothing here is published; this workbook is handed over as a file.</t>
         </is>
       </c>
     </row>
@@ -530,165 +530,172 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="39" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Relationship numbers are append-only. A new relationship is appended (R15, R16, …) and never inserted, so R1–R14 keep the numbers cited elsewhere — including in the Hebrew workbook. Entity numbers (E1–E14) carry no such guarantee: nothing cross-references them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="8" customHeight="1">
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="3" t="inlineStr">
+          <t>Relationship numbers are append-only. A new relationship is appended (R15, R16, R17, R18, …) and never inserted, so R1–R16 keep the numbers cited elsewhere — including in the Hebrew workbook, which is frozen at an older state. Entity numbers (E1–E16) carry no such guarantee: nothing cross-references them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>The DECISIONS sheet now carries two kinds of row. A D-number is a shaping decision made inside this workbook. An A-number is a repository architecture decision from tasks/plan.md, reproduced here because it shapes these tables — A8 is the first. Reproduced under its own number rather than renumbered, so one decision keeps one name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="8" customHeight="1">
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>The one idea that keeps this simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>A building is not a bag of apartments. It is a set of SPACES — some private and leasable (apartments), some shared (lobby, stairwell, roof), some technical (pump room, electrical room), some outside (garden, gate), and some assignable (parking bays, storage rooms). Everything that can break, be inspected or be handed over is an ASSET, and every asset sits in exactly one space.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>A building is not a bag of apartments. It is a set of SPACES — some private and leasable (apartments), some shared (lobby, stairwell, roof), some technical (pump room, electrical room), some outside (garden, gate), and some assignable (parking bays, storage rooms). Everything that can break, be inspected or be handed over is an ASSET, and every asset sits in exactly one space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>That means common areas, safety equipment and operational utilities do NOT become three new families of tables. Common areas are spaces. Fire extinguishers, sprinklers, pumps, elevators and boilers are assets that happen to sit in a shared or technical space. One table for places, one for things. Every query about a building is then the same query.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="8" customHeight="1">
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="3" t="inlineStr">
+    <row r="12" ht="8" customHeight="1">
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Why that shape pays for itself immediately</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Responsibility falls out of it. An asset in a UNIT space can be tenant, operator or contractor. An asset in a COMMON, TECHNICAL or EXTERIOR space is never the tenant's — the rule reads the space kind and stops. We get half the responsibility matrix from the location of the thing, without writing a rule per asset type.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="8" customHeight="1">
-      <c r="B14" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="15" ht="8" customHeight="1">
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Five rules the draft obeys everywhere</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17" ht="39" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>1.  The current tenant is a VIEW, never a column. A unit does not hold a tenant. A tenancy holds a unit and a date range, and 'who lives there' is resolved as today ∈ [start, end]. This is what makes tenant isolation safe — see the Relationships sheet, row R6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2.  Nothing is overwritten. A new lease does not replace the old one, it follows it. A corrected rule supersedes by date. Last year's decision can still be reconstructed.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>2.  Nothing is overwritten. A new lease does not replace the old one, it follows it. A corrected rule supersedes by date. Last year's decision can still be reconstructed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>3.  No money. Not one amount, anywhere in this model. Rent, arrears and invoices stay in Priority. We record whether an obligation is SATISFIED, never what it costs.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>4.  Every fact points at the paper it came from. Documents are linked, not summarised.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>5.  Structure carries meaning, so text does not have to. Where a field is a short fixed list, the list is in the draft. Free text is the exception.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="22" ht="8" customHeight="1">
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>What is deliberately NOT in this pass</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="52" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Service calls, visits, providers, the state machine and the agent. You asked for building then unit, and those sit downstream of both. Provider appears once, as a stub, only because an asset under warranty has to point at whoever is on the hook for it during תקופת הבדק. Nothing else about the service loop is touched.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Also absent: rent, deposits, arrears, indexation, and anything an accountant would recognise. That is Priority's, permanently.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="8" customHeight="1">
-      <c r="B25" t="inlineStr"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="26" ht="8" customHeight="1">
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>How to read the sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>ENTITIES — everything that exists, and what one row of each actually is. Read this first; if a grain is wrong, everything downstream is wrong.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>RELATIONSHIPS — the heart of it. Every line between two entities, in plain words, with what breaks if we get it backwards.</t>
+          <t>ENTITIES — everything that exists, and what one row of each actually is. Read this first; if a grain is wrong, everything downstream is wrong.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>RELATIONSHIPS — the heart of it. Every line between two entities, in plain words, with what breaks if we get it backwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>FIELDS — the minimum each entity carries. Grouped by entity, filterable. This is the sheet that grows: add rows, don't reshape.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="39" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="31" ht="39" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ADMIN VIEWS — what an admin actually sees on a building screen, a unit screen and the settings screen, and which parts are stored versus derived. The test of the model is whether these screens fall out of it without special cases.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>DECISIONS — the six shaping decisions, each stated as the rule it creates and why that rule holds. Kept in the workbook so they are read alongside the tables they explain.</t>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>DECISIONS — the six shaping decisions plus A8, each stated as the rule it creates and why that rule holds. Kept in the workbook so they are read alongside the tables they explain.</t>
         </is>
       </c>
     </row>
@@ -703,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1118,8 +1125,62 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>One kind of document that can be filed, managed as a row.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>The catalogue behind Document. Turns 'we now also receive a ועד בית agreement' from a migration and a release into a seed row. Deactivated, never deleted — filed documents still point at it.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>NEW — A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>One field a document type declares, in one version of its schema.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>What we expect to read off a document of that type, and what to call it. Versioned by effective_from, so a value extracted under version 3 of a lease schema is still explicable a year later.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>NEW — A8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1130,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1853,8 +1914,92 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>is typed by</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>N : 1</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Document.document_type_id → DocumentType.document_type_id</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>NEW, A8. The kind of a document is a row in a catalogue, not a value in an enum. Adding 'ועד בית agreement' or a municipality's own ארנונה format is a seed row: no migration, no deploy, and the document is filed, citable and searchable the same day.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>As an enum, every new document type is a schema change — and document types keep arriving, one per tender addendum and one per municipality. A retired type is deactivated and never deleted, for R16's reason: filed documents still point at it, and those are the records a dispute reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>declares many</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>1 : N, versioned</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField.document_type_id → DocumentType.document_type_id, unique (document_type_id, field_key, effective_from)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>NEW, A8. A type declares the fields we expect to read off it, and each declaration is dated. Correcting or extending a schema appends a new row and closes the old one; it never edits what a previous version said.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Without effective_from, correcting a schema silently rewrites the meaning of every value already extracted under the old one. The extracted value points at the exact DocumentTypeField row that governed it, which is what makes 'why does this lease say 14 months' answerable a year later.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1865,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4785,12 +4930,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>type_key</t>
+          <t>document_type_id</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -4798,15 +4943,19 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr"/>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>FK → DocumentType</t>
+        </is>
+      </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>lease · lease_amendment · termination_notice · arnona · insurance · id · bank_guarantee · handover_protocol · inspection_certificate</t>
+          <t>Which kind of document this is.</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>The first eight are already agreed. inspection_certificate is new here, and needed by SAFETY assets.</t>
+          <t>CHANGED BY A8 — was a fixed type_key enum of nine values, now points at an admin-managed row. See R17. The nine become the seed rows of E15.</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4986,11 @@
           <t>Our copy, in our object storage.</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>The path carries the place and never the people, keyed by id rather than a transliterated address. Slice 3.2.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -4847,7 +5000,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>sha256</t>
+          <t>file_hash</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -4863,12 +5016,12 @@
       <c r="E103" s="6" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Hash taken at ingest.</t>
+          <t>Hash taken at ingest, immutable thereafter.</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Proves the copy is the file we read.</t>
+          <t>Proves the copy is the file we read. Named file_hash and not sha256: SPEC-flows.md A1 names it that, and the field names the purpose rather than this year's algorithm.</t>
         </is>
       </c>
     </row>
@@ -5221,8 +5374,579 @@
         </is>
       </c>
     </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>E15 · DOCUMENTTYPE — the catalogue behind Document (A8)</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="8" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>document_type_id</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>type_key</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Stable machine key. Nine seed rows: lease · lease_amendment · termination_notice · arnona · insurance · id · bank_guarantee · handover_protocol · inspection_certificate.</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>The first eight are the Data Model's. inspection_certificate is the ninth, needed by SAFETY assets and by the compliance tab. Never renamed and never reused — filed documents point at it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>label_he</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr"/>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>What the admin sees and chooses from: חוזה שכירות · נספח · הודעת סיום · ארנונה · ביטוח · תעודת זהות · ערבות בנקאית · פרוטוקול מסירה · תעודת בדיקה.</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>label_en</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr"/>
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>verification_terms</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>text[]</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr"/>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>Marker terms a document of this type is expected to contain.</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>The cheap guard in slice 3.3 — right slot, wrong file — reads this and nothing else. It lives on the type row rather than in code, or a new type would arrive with no guard until the next release, and A8 would be true of the catalogue and false of everything that uses it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr"/>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Retired types stay as rows and stop appearing in the 'file a document' list.</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>NEVER delete a type. A9: the admin screen for this catalogue lands in month two; until then we add rows through seeds, which is the same mechanism with a different hand on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr"/>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>NO promotes_to. NO validation_rules. NO renewal_cadence.</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>A8 deliberately: a promotes_to column would make promotion a row, and promotion is the half that is governed — it costs a migration and a reviewed mapping because those columns are what the isolation join, the responsibility matrix and the state machine read. Renewal cadence and 'what is missing' belong to DocumentRequirement, which is month two's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>E16 · DOCUMENTTYPEFIELD — what a type declares, in one version (A8)</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>document_type_field_id</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>document_type_id</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>FK → DocumentType</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>See R18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>field_key</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>unique part</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>Stable machine key within the type: start_date, end_date, tenant_name, apartment_number.</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>Unique on (document_type_id, field_key, effective_from) — the same field, redeclared, is a new row and not an edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>label_he</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr"/>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>What a reviewer sees beside the value on the page.</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>value_type</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr"/>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>TEXT · NUMBER · DATE · BOOLEAN · ENUM</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>No MONEY type, and no money field is seeded. READ ME rule 3 binds hardest at promotion: no amount is ever a column on a business record, and no amount is ever quoted to a tenant — the golden set carries that as a standing refusal case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>is_required</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr"/>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>Is this field expected in a document of this type?</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>A missing required field is a RESULT, not an error. A lease commonly names no guarantor — SPEC-flows A2 — and extraction returning nothing there is correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>extraction_hint</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr"/>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>The Hebrew phrasing as printed on the form, to look for on the page.</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>A hint, never a key. Same rule as a Drive path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>effective_from</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr"/>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>The version. This row governs values extracted on or after this date.</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>A8, for policy_version_id's reason. The extracted value points at THIS row, so A8's schema_version_id is document_type_field_id and there is no separate version entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>effective_to</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr"/>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>Null = the current declaration.</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>Closing a row never edits it. Nothing is overwritten — READ ME rule 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr"/>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>NO target column, NO promotion mapping.</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Capture is open; promotion is governed. The mapping from a captured field to a typed column is a migration and a reviewed mapping, not a row an admin can add on a Tuesday. See A8.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G116"/>
+  <autoFilter ref="A1:G135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5233,7 +5957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5757,109 +6481,109 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Guarded</t>
+          <t>Admin-managed</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Asset types — the list the responsibility matrix keys on</t>
+          <t>Document types and their fields — add a type, declare what it carries, retire it</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Asset.asset_type</t>
+          <t>DocumentType + DocumentTypeField</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Stored, governed</t>
+          <t>Stored</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>NOT on this screen. Editing it edits policy, and policy is versioned with effective_from so a dispute a year later still resolves. Changes go through the same route as a rule change.</t>
+          <t>A8, and A9 for the timing: the mechanism is a row from week 3, the screen lands in month two beside the obligation-types screen whose pattern it shares. Until then we add rows through seeds. Adding a field is safe here precisely because it cannot promote itself to a column.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Guarded</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Asset types — the list the responsibility matrix keys on</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Asset.asset_type</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Stored, governed</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>NOT on this screen. Editing it edits policy, and policy is versioned with effective_from so a dispute a year later still resolves. Changes go through the same route as a rule change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Guarantor reachability</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>TenancyParty.is_service_contact</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Constraint</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Not a setting at all. D4 made it a database rule so there is no switch to find.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>THE TEST — if the model is right, these are all one query each</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Who lives in unit 12 today?</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Unit → Tenancy (today in range) → TenancyParty → Party</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>No stored pointer anywhere.</t>
-        </is>
-      </c>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>This phone number just messaged us — which unit, if any?</t>
+          <t>Who lives in unit 12 today?</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>PartyContact (valid today) → Party → TenancyParty → Tenancy (active) → Unit</t>
+          <t>Unit → Tenancy (today in range) → TenancyParty → Party</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -5869,24 +6593,24 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Five hops, all SQL, before any model call. The isolation join.</t>
+          <t>No stored pointer anywhere.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>What is overdue for inspection in this building?</t>
+          <t>This phone number just messaged us — which unit, if any?</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Space → Asset where next_inspection_due &lt; today</t>
+          <t>PartyContact (valid today) → Party → TenancyParty → Tenancy (active) → Unit</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -5896,24 +6620,24 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Works because assets hang on spaces.</t>
+          <t>Five hops, all SQL, before any model call. The isolation join.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Is this broken thing the tenant's problem?</t>
+          <t>What is overdue for inspection in this building?</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Asset → Space.space_kind + Asset.warranty_end_date + Tenancy.terms_profile_id</t>
+          <t>Space → Asset where next_inspection_due &lt; today</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -5923,24 +6647,24 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Three inputs, no AI, fully inspectable a year later.</t>
+          <t>Works because assets hang on spaces.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Which leases end in the next 60 days, across 1,500 units?</t>
+          <t>Is this broken thing the tenant's problem?</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Tenancy where end_date between today and +60</t>
+          <t>Asset → Space.space_kind + Asset.warranty_end_date + Tenancy.terms_profile_id</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -5950,24 +6674,24 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>One index, whole portfolio.</t>
+          <t>Three inputs, no AI, fully inspectable a year later.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Show me every apartment with no insurance on file.</t>
+          <t>Which leases end in the next 60 days, across 1,500 units?</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Unit → Tenancy (active) → Obligation where type = CONTENTS_INSURANCE and status ≠ SATISFIED</t>
+          <t>Tenancy where end_date between today and +60</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -5977,39 +6701,66 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>The kind of question that is impossible today and trivial here.</t>
+          <t>One index, whole portfolio.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Show me every apartment with no insurance on file.</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Unit → Tenancy (active) → Obligation where type = CONTENTS_INSURANCE and status ≠ SATISFIED</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>The kind of question that is impossible today and trivial here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Which bay is assigned to unit 12, and who serviced its gate motor?</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Unit.parking_space_id → Space → Asset</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>New from D3, and free — a bay is a place like any other.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6020,7 +6771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6219,8 +6970,35 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>What does it cost to add a document type, or a field to one?</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Capture is open; promotion is governed.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>A type is a DocumentType row (E15, R17) and a field is a DocumentTypeField row (E16, R18): zero migrations, zero deploys, and the value is citable and searchable the moment it is extracted. DocumentTypeField is versioned by effective_from, and an extracted value points at the exact row that governed it. Promotion — an extracted value becoming a typed column such as Tenancy.start_date or Asset.warranty_end_date — costs a migration and a reviewed mapping. There is deliberately no promotes_to column anywhere in E15 or E16.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>This is tasks/plan.md's A8, reproduced here under its own number because it shapes these tables. It is not a new principle: it is D5 and the asset_type rule applied to documents. Document types keep arriving — a tender's addendum, a municipality's ארנונה format, a ועד בית agreement — and none of them may cost a release. But the columns promotion writes are what the isolation join, the responsibility matrix and the state machine read, so 'an admin added a field on Tuesday and the responsibility answer changed' stays impossible by construction, exactly as it is for asset_type.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/model/dona-building-unit-model-draft.xlsx
+++ b/docs/model/dona-building-unit-model-draft.xlsx
@@ -4561,12 +4561,12 @@
       <c r="E88" s="6" t="inlineStr"/>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>The specific kind, from a controlled list.</t>
+          <t>FIXTURE: AC · WATER_HEATER · OVEN · BLINDS · PLUMBING. SAFETY: EXTINGUISHER · SPRINKLER · SMOKE_DETECTOR · EMERGENCY_LIGHT · MAMAD_BLAST_DOOR. UTILITY: PUMP · ELEVATOR · BOILER · GATE_MOTOR · INTERCOM · METER.</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>This is the field the responsibility matrix keys on. It must be a list, never free text — and unlike obligation types, this list is governed, not admin-editable. Editing it edits policy.</t>
+          <t>This is the field the responsibility matrix keys on. It must be a list, never free text — and unlike obligation types, this list is governed, not admin-editable. Editing it edits policy. The pairs are the workbook's own class examples, enumerated rather than left as prose, because a governed list that is nowhere written down is not governed. A composite CHECK on the pair stops a SAFETY sprinkler being filed as a FIXTURE.</t>
         </is>
       </c>
     </row>

--- a/docs/model/dona-building-unit-model-draft.xlsx
+++ b/docs/model/dona-building-unit-model-draft.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ENTITIES'!$A$1:$E$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RELATIONSHIPS'!$A$1:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FIELDS'!$A$1:$G$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FIELDS'!$A$1:$G$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ADMIN VIEWS'!$A$1:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DECISIONS'!$A$1:$E$8</definedName>
   </definedNames>
@@ -2010,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5137,47 +5137,51 @@
       <c r="F107" s="6" t="inlineStr"/>
       <c r="G107" s="6" t="inlineStr"/>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>verification_verdict</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>verified · unverified · unguarded</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>Slice 3.6. The 3.3 guard's result, made a property of a list so a scan does not look identical to a lease whose marker terms were found. Not figure 5's state (RECEIVED / EXTRACTED / ACCEPTED / REJECTED), which is still omitted: refused uploads still leave no row. 4.1 may later move unverified → verified once OCR gives the file a text layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>E13 · DOCUMENTLINK — one document, several bindings</t>
         </is>
       </c>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>DocumentLink</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>document_id</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>PK part, FK</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr"/>
-      <c r="G109" s="6" t="inlineStr"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -5187,12 +5191,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>entity_type</t>
+          <t>document_id</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -5200,17 +5204,13 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr"/>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>PROJECT · BUILDING · SPACE · UNIT · TENANCY · PARTY · ASSET · OBLIGATION</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>PROJECT added by D2 — a tender document belongs to the project, not to any one building.</t>
-        </is>
-      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>PK part, FK</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>entity_type</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -5233,13 +5233,17 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>PK part</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr"/>
-      <c r="G111" s="6" t="inlineStr"/>
+      <c r="E111" s="6" t="inlineStr"/>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>PROJECT · BUILDING · SPACE · UNIT · TENANCY · PARTY · ASSET · OBLIGATION</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>PROJECT added by D2 — a tender document belongs to the project, not to any one building.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -5249,72 +5253,72 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>PK part</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>DocumentLink</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
           <t>link_role</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr"/>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="E113" s="6" t="inlineStr"/>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <t>SIGNATORY · SUBJECT · EVIDENCE · SOURCE</t>
         </is>
       </c>
-      <c r="G112" s="6" t="inlineStr">
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>A lease links to two parties as SIGNATORY and to the unit as SUBJECT.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>E14 · PROVIDER — stub only, out of scope this pass</t>
         </is>
       </c>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>provider_id</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr"/>
-      <c r="G114" s="6" t="inlineStr"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -5324,12 +5328,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>provider_id</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -5337,7 +5341,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr"/>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="F115" s="6" t="inlineStr"/>
       <c r="G115" s="6" t="inlineStr"/>
     </row>
@@ -5349,72 +5357,68 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr"/>
+      <c r="F116" s="6" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
           <t>provider_kind</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr"/>
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <t>IN_HOUSE_CREW · CONTRACTOR · DEVELOPER_WARRANTY</t>
         </is>
       </c>
-      <c r="G116" s="6" t="inlineStr">
+      <c r="G117" s="6" t="inlineStr">
         <is>
           <t>Present only to make R11 resolvable. Everything else about providers waits.</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>E15 · DOCUMENTTYPE — the catalogue behind Document (A8)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="n"/>
-      <c r="C117" s="8" t="n"/>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="8" t="n"/>
-      <c r="F117" s="8" t="n"/>
-      <c r="G117" s="8" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>DocumentType</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>document_type_id</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr"/>
-      <c r="G118" s="6" t="inlineStr"/>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -5424,12 +5428,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>type_key</t>
+          <t>document_type_id</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -5439,19 +5443,11 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>Stable machine key. Nine seed rows: lease · lease_amendment · termination_notice · arnona · insurance · id · bank_guarantee · handover_protocol · inspection_certificate.</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>The first eight are the Data Model's. inspection_certificate is the ninth, needed by SAFETY assets and by the compliance tab. Never renamed and never reused — filed documents point at it.</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr"/>
+      <c r="G119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -5461,7 +5457,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>label_he</t>
+          <t>type_key</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -5474,13 +5470,21 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr"/>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>What the admin sees and chooses from: חוזה שכירות · נספח · הודעת סיום · ארנונה · ביטוח · תעודת זהות · ערבות בנקאית · פרוטוקול מסירה · תעודת בדיקה.</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
+          <t>Stable machine key. Nine seed rows: lease · lease_amendment · termination_notice · arnona · insurance · id · bank_guarantee · handover_protocol · inspection_certificate.</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>The first eight are the Data Model's. inspection_certificate is the ninth, needed by SAFETY assets and by the compliance tab. Never renamed and never reused — filed documents point at it.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -5490,7 +5494,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>label_en</t>
+          <t>label_he</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -5500,11 +5504,15 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr"/>
-      <c r="F121" s="6" t="inlineStr"/>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>What the admin sees and chooses from: חוזה שכירות · נספח · הודעת סיום · ארנונה · ביטוח · תעודת זהות · ערבות בנקאית · פרוטוקול מסירה · תעודת בדיקה.</t>
+        </is>
+      </c>
       <c r="G121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
@@ -5515,12 +5523,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>verification_terms</t>
+          <t>label_en</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>text[]</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -5529,16 +5537,8 @@
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>Marker terms a document of this type is expected to contain.</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>The cheap guard in slice 3.3 — right slot, wrong file — reads this and nothing else. It lives on the type row rather than in code, or a new type would arrive with no guard until the next release, and A8 would be true of the catalogue and false of everything that uses it.</t>
-        </is>
-      </c>
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -5548,28 +5548,28 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>verification_terms</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>text[]</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>Retired types stay as rows and stop appearing in the 'file a document' list.</t>
+          <t>Marker terms a document of this type is expected to contain.</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>NEVER delete a type. A9: the admin screen for this catalogue lands in month two; until then we add rows through seeds, which is the same mechanism with a different hand on it.</t>
+          <t>The cheap guard in slice 3.3 — right slot, wrong file — reads this and nothing else. It lives on the type row rather than in code, or a new type would arrive with no guard until the next release, and A8 would be true of the catalogue and false of everything that uses it.</t>
         </is>
       </c>
     </row>
@@ -5581,72 +5581,76 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr">
         <is>
+          <t>Retired types stay as rows and stop appearing in the 'file a document' list.</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>NEVER delete a type. A9: the admin screen for this catalogue lands in month two; until then we add rows through seeds, which is the same mechanism with a different hand on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>DocumentType</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr"/>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
           <t>NO promotes_to. NO validation_rules. NO renewal_cadence.</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G125" s="6" t="inlineStr">
         <is>
           <t>A8 deliberately: a promotes_to column would make promotion a row, and promotion is the half that is governed — it costs a migration and a reviewed mapping because those columns are what the isolation join, the responsibility matrix and the state machine read. Renewal cadence and 'what is missing' belong to DocumentRequirement, which is month two's.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>E16 · DOCUMENTTYPEFIELD — what a type declares, in one version (A8)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="n"/>
-      <c r="C125" s="8" t="n"/>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="8" t="n"/>
-      <c r="G125" s="8" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>DocumentTypeField</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>document_type_field_id</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr"/>
-      <c r="G126" s="6" t="inlineStr"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
+      <c r="G126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -5656,7 +5660,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>document_type_id</t>
+          <t>document_type_field_id</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -5671,15 +5675,11 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>FK → DocumentType</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>See R18.</t>
-        </is>
-      </c>
+      <c r="G127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>field_key</t>
+          <t>document_type_id</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -5704,17 +5704,13 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>unique part</t>
-        </is>
-      </c>
-      <c r="F128" s="6" t="inlineStr">
-        <is>
-          <t>Stable machine key within the type: start_date, end_date, tenant_name, apartment_number.</t>
-        </is>
-      </c>
+          <t>FK → DocumentType</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr"/>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Unique on (document_type_id, field_key, effective_from) — the same field, redeclared, is a new row and not an edit.</t>
+          <t>See R18.</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5722,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>label_he</t>
+          <t>field_key</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -5739,13 +5735,21 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr"/>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>unique part</t>
+        </is>
+      </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>What a reviewer sees beside the value on the page.</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr"/>
+          <t>Stable machine key within the type: start_date, end_date, tenant_name, apartment_number.</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>Unique on (document_type_id, field_key, effective_from) — the same field, redeclared, is a new row and not an edit.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -5755,12 +5759,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>value_type</t>
+          <t>label_he</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -5771,14 +5775,10 @@
       <c r="E130" s="6" t="inlineStr"/>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>TEXT · NUMBER · DATE · BOOLEAN · ENUM</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>No MONEY type, and no money field is seeded. READ ME rule 3 binds hardest at promotion: no amount is ever a column on a business record, and no amount is ever quoted to a tenant — the golden set carries that as a standing refusal case.</t>
-        </is>
-      </c>
+          <t>What a reviewer sees beside the value on the page.</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>is_required</t>
+          <t>value_type</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -5804,12 +5804,12 @@
       <c r="E131" s="6" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>Is this field expected in a document of this type?</t>
+          <t>TEXT · NUMBER · DATE · BOOLEAN · ENUM</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>A missing required field is a RESULT, not an error. A lease commonly names no guarantor — SPEC-flows A2 — and extraction returning nothing there is correct.</t>
+          <t>No MONEY type, and no money field is seeded. READ ME rule 3 binds hardest at promotion: no amount is ever a column on a business record, and no amount is ever quoted to a tenant — the golden set carries that as a standing refusal case.</t>
         </is>
       </c>
     </row>
@@ -5821,28 +5821,28 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>extraction_hint</t>
+          <t>is_required</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>The Hebrew phrasing as printed on the form, to look for on the page.</t>
+          <t>Is this field expected in a document of this type?</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>A hint, never a key. Same rule as a Drive path.</t>
+          <t>A missing required field is a RESULT, not an error. A lease commonly names no guarantor — SPEC-flows A2 — and extraction returning nothing there is correct.</t>
         </is>
       </c>
     </row>
@@ -5854,28 +5854,28 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>effective_from</t>
+          <t>extraction_hint</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>The version. This row governs values extracted on or after this date.</t>
+          <t>The Hebrew phrasing as printed on the form, to look for on the page.</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>A8, for policy_version_id's reason. The extracted value points at THIS row, so A8's schema_version_id is document_type_field_id and there is no separate version entity.</t>
+          <t>A hint, never a key. Same rule as a Drive path.</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>effective_to</t>
+          <t>effective_from</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -5897,18 +5897,18 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Null = the current declaration.</t>
+          <t>The version. This row governs values extracted on or after this date.</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Closing a row never edits it. Nothing is overwritten — READ ME rule 2.</t>
+          <t>A8, for policy_version_id's reason. The extracted value points at THIS row, so A8's schema_version_id is document_type_field_id and there is no separate version entity.</t>
         </is>
       </c>
     </row>
@@ -5920,33 +5920,66 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>effective_to</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr">
         <is>
+          <t>Null = the current declaration.</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Closing a row never edits it. Nothing is overwritten — READ ME rule 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>DocumentTypeField</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr"/>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
           <t>NO target column, NO promotion mapping.</t>
         </is>
       </c>
-      <c r="G135" s="6" t="inlineStr">
+      <c r="G136" s="6" t="inlineStr">
         <is>
           <t>Capture is open; promotion is governed. The mapping from a captured field to a typed column is a migration and a reviewed mapping, not a row an admin can add on a Tuesday. See A8.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G135"/>
+  <autoFilter ref="A1:G136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
